--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,3619 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125889850</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>401064</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7064314</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125890366</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75058</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>401063</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7064359</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125890358</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>401130</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7064629</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125889832</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75066</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>401085</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7064265</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125890359</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>401146</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7064592</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125890363</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>401196</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7064572</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125890357</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>401016</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7064444</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125890352</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79126</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>401129</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7064590</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125890351</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>401128</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7064635</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125889830</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75066</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>401228</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7064385</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125889848</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>401108</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7064676</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125890341</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75066</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>401174</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7064577</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125889841</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>401024</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7064328</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125889831</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75066</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>401096</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7064277</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125889852</v>
+      </c>
+      <c r="B17" t="n">
+        <v>88626</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>510</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>401144</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7064600</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125889839</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>401042</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7064326</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125889836</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>401044</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7064691</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125889847</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>401042</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7064458</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125890344</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91914</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>401026</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7064458</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125890350</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>401071</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7064285</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125889838</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>401179</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7064356</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125889834</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91220</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>401077</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7064505</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125889842</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91577</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>401009</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7064292</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125889837</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>401214</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7064364</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125889849</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>401254</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7064480</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125889829</v>
+      </c>
+      <c r="B28" t="n">
+        <v>75066</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>401164</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7064559</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125890345</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>401083</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7064287</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125889844</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>401002</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7064296</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125890348</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>401037</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7064318</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125889843</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>401114</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7064640</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125889833</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91185</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>401150</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7064603</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125889851</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>401035</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7064310</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125890347</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91170</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>112</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>401276</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7064509</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125890353</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>401111</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7064685</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125890365</v>
+      </c>
+      <c r="B37" t="n">
+        <v>75058</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>308</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>401081</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7064302</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125890342</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91185</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>401266</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7064514</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125890362</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91238</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Beljom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>400981</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7064305</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889841</v>
+        <v>125889831</v>
       </c>
       <c r="B15" t="n">
-        <v>58019</v>
+        <v>75066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401024</v>
+        <v>401096</v>
       </c>
       <c r="R15" t="n">
-        <v>7064328</v>
+        <v>7064277</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889831</v>
+        <v>125889852</v>
       </c>
       <c r="B16" t="n">
-        <v>75066</v>
+        <v>88626</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401096</v>
+        <v>401144</v>
       </c>
       <c r="R16" t="n">
-        <v>7064277</v>
+        <v>7064600</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889852</v>
+        <v>125889841</v>
       </c>
       <c r="B17" t="n">
-        <v>88626</v>
+        <v>58019</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401144</v>
+        <v>401024</v>
       </c>
       <c r="R17" t="n">
-        <v>7064600</v>
+        <v>7064328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>75058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R3" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125890366</v>
+        <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>75058</v>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401063</v>
+        <v>401064</v>
       </c>
       <c r="R4" t="n">
-        <v>7064359</v>
+        <v>7064314</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -988,7 +988,7 @@
         <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>125890359</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890363</v>
+        <v>125890352</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>79126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401196</v>
+        <v>401129</v>
       </c>
       <c r="R8" t="n">
-        <v>7064572</v>
+        <v>7064590</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890357</v>
+        <v>125890351</v>
       </c>
       <c r="B9" t="n">
-        <v>91238</v>
+        <v>80071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401016</v>
+        <v>401128</v>
       </c>
       <c r="R9" t="n">
-        <v>7064444</v>
+        <v>7064635</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890352</v>
+        <v>125890363</v>
       </c>
       <c r="B10" t="n">
-        <v>79126</v>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401129</v>
+        <v>401196</v>
       </c>
       <c r="R10" t="n">
-        <v>7064590</v>
+        <v>7064572</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890351</v>
+        <v>125890357</v>
       </c>
       <c r="B11" t="n">
-        <v>80071</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401128</v>
+        <v>401016</v>
       </c>
       <c r="R11" t="n">
-        <v>7064635</v>
+        <v>7064444</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889831</v>
+        <v>125889852</v>
       </c>
       <c r="B15" t="n">
-        <v>75066</v>
+        <v>88633</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401096</v>
+        <v>401144</v>
       </c>
       <c r="R15" t="n">
-        <v>7064277</v>
+        <v>7064600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B16" t="n">
-        <v>88626</v>
+        <v>75066</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R16" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2249,7 +2249,7 @@
         <v>125889839</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125890344</v>
       </c>
       <c r="B21" t="n">
-        <v>91914</v>
+        <v>91921</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>125889834</v>
       </c>
       <c r="B24" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>125889842</v>
       </c>
       <c r="B25" t="n">
-        <v>91577</v>
+        <v>91584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125889844</v>
+        <v>125890348</v>
       </c>
       <c r="B30" t="n">
-        <v>91238</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401002</v>
+        <v>401037</v>
       </c>
       <c r="R30" t="n">
-        <v>7064296</v>
+        <v>7064318</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,12 +3501,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3525,32 +3531,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125890348</v>
+        <v>125889844</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>91245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3560,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401037</v>
+        <v>401002</v>
       </c>
       <c r="R31" t="n">
-        <v>7064318</v>
+        <v>7064296</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3598,18 +3604,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>125889843</v>
       </c>
       <c r="B32" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>125889833</v>
       </c>
       <c r="B33" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>91177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R34" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B35" t="n">
-        <v>91170</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R35" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125890353</v>
+        <v>125890365</v>
       </c>
       <c r="B36" t="n">
-        <v>80070</v>
+        <v>75058</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401111</v>
+        <v>401081</v>
       </c>
       <c r="R36" t="n">
-        <v>7064685</v>
+        <v>7064302</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890365</v>
+        <v>125890353</v>
       </c>
       <c r="B37" t="n">
-        <v>75058</v>
+        <v>80070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,21 +4124,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401081</v>
+        <v>401111</v>
       </c>
       <c r="R37" t="n">
-        <v>7064302</v>
+        <v>7064685</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890342</v>
+        <v>125890362</v>
       </c>
       <c r="B38" t="n">
-        <v>91185</v>
+        <v>91245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401266</v>
+        <v>400981</v>
       </c>
       <c r="R38" t="n">
-        <v>7064514</v>
+        <v>7064305</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890362</v>
+        <v>125890342</v>
       </c>
       <c r="B39" t="n">
-        <v>91238</v>
+        <v>91192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>400981</v>
+        <v>401266</v>
       </c>
       <c r="R39" t="n">
-        <v>7064305</v>
+        <v>7064514</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125890348</v>
+        <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>91245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401037</v>
+        <v>401002</v>
       </c>
       <c r="R30" t="n">
-        <v>7064318</v>
+        <v>7064296</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,18 +3501,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3531,7 +3525,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889844</v>
+        <v>125889843</v>
       </c>
       <c r="B31" t="n">
         <v>91245</v>
@@ -3566,10 +3560,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401002</v>
+        <v>401114</v>
       </c>
       <c r="R31" t="n">
-        <v>7064296</v>
+        <v>7064640</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3628,32 +3622,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889843</v>
+        <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91245</v>
+        <v>91192</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3657,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401114</v>
+        <v>401150</v>
       </c>
       <c r="R32" t="n">
-        <v>7064640</v>
+        <v>7064603</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,10 +3719,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125889833</v>
+        <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>91192</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,21 +3730,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3760,10 +3754,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401150</v>
+        <v>401037</v>
       </c>
       <c r="R33" t="n">
-        <v>7064603</v>
+        <v>7064318</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3798,12 +3792,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>125890366</v>
       </c>
       <c r="B3" t="n">
-        <v>75058</v>
+        <v>75059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>125889832</v>
       </c>
       <c r="B6" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>125890359</v>
       </c>
       <c r="B7" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890352</v>
+        <v>125890363</v>
       </c>
       <c r="B8" t="n">
-        <v>79126</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401129</v>
+        <v>401196</v>
       </c>
       <c r="R8" t="n">
-        <v>7064590</v>
+        <v>7064572</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890351</v>
+        <v>125890357</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>91246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401128</v>
+        <v>401016</v>
       </c>
       <c r="R9" t="n">
-        <v>7064635</v>
+        <v>7064444</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890363</v>
+        <v>125890351</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>80072</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401196</v>
+        <v>401128</v>
       </c>
       <c r="R10" t="n">
-        <v>7064572</v>
+        <v>7064635</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890357</v>
+        <v>125890352</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>79127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401016</v>
+        <v>401129</v>
       </c>
       <c r="R11" t="n">
-        <v>7064444</v>
+        <v>7064590</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1667,7 +1667,7 @@
         <v>125889830</v>
       </c>
       <c r="B12" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>125889848</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>125890341</v>
       </c>
       <c r="B14" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B15" t="n">
-        <v>88633</v>
+        <v>75067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R15" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889831</v>
+        <v>125889852</v>
       </c>
       <c r="B16" t="n">
-        <v>75066</v>
+        <v>88637</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401096</v>
+        <v>401144</v>
       </c>
       <c r="R16" t="n">
-        <v>7064277</v>
+        <v>7064600</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2152,7 +2152,7 @@
         <v>125889841</v>
       </c>
       <c r="B17" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>125889839</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125889847</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125890344</v>
       </c>
       <c r="B21" t="n">
-        <v>91921</v>
+        <v>91922</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889834</v>
+        <v>125889842</v>
       </c>
       <c r="B24" t="n">
-        <v>91227</v>
+        <v>91585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401077</v>
+        <v>401009</v>
       </c>
       <c r="R24" t="n">
-        <v>7064505</v>
+        <v>7064292</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889842</v>
+        <v>125889834</v>
       </c>
       <c r="B25" t="n">
-        <v>91584</v>
+        <v>91228</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401009</v>
+        <v>401077</v>
       </c>
       <c r="R25" t="n">
-        <v>7064292</v>
+        <v>7064505</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3030,7 +3030,7 @@
         <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>125889849</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>125889829</v>
       </c>
       <c r="B28" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>125889843</v>
       </c>
       <c r="B31" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B34" t="n">
-        <v>91177</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R34" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>91178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R35" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125890365</v>
+        <v>125890353</v>
       </c>
       <c r="B36" t="n">
-        <v>75058</v>
+        <v>80071</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401081</v>
+        <v>401111</v>
       </c>
       <c r="R36" t="n">
-        <v>7064302</v>
+        <v>7064685</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890353</v>
+        <v>125890365</v>
       </c>
       <c r="B37" t="n">
-        <v>80070</v>
+        <v>75059</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,21 +4124,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401111</v>
+        <v>401081</v>
       </c>
       <c r="R37" t="n">
-        <v>7064685</v>
+        <v>7064302</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4213,7 +4213,7 @@
         <v>125890362</v>
       </c>
       <c r="B38" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>125890342</v>
       </c>
       <c r="B39" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -1470,32 +1470,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890351</v>
+        <v>125890352</v>
       </c>
       <c r="B10" t="n">
-        <v>80072</v>
+        <v>79127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401128</v>
+        <v>401129</v>
       </c>
       <c r="R10" t="n">
-        <v>7064635</v>
+        <v>7064590</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890352</v>
+        <v>125890351</v>
       </c>
       <c r="B11" t="n">
-        <v>79127</v>
+        <v>80072</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401129</v>
+        <v>401128</v>
       </c>
       <c r="R11" t="n">
-        <v>7064590</v>
+        <v>7064635</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125889848</v>
+        <v>125890341</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401108</v>
+        <v>401174</v>
       </c>
       <c r="R13" t="n">
-        <v>7064676</v>
+        <v>7064577</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125890341</v>
+        <v>125889848</v>
       </c>
       <c r="B14" t="n">
-        <v>75067</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1869,21 +1869,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>401174</v>
+        <v>401108</v>
       </c>
       <c r="R14" t="n">
-        <v>7064577</v>
+        <v>7064676</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889831</v>
+        <v>125889852</v>
       </c>
       <c r="B15" t="n">
-        <v>75067</v>
+        <v>88637</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401096</v>
+        <v>401144</v>
       </c>
       <c r="R15" t="n">
-        <v>7064277</v>
+        <v>7064600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B16" t="n">
-        <v>88637</v>
+        <v>75067</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R16" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889841</v>
+        <v>125889839</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>98355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401024</v>
+        <v>401042</v>
       </c>
       <c r="R17" t="n">
-        <v>7064328</v>
+        <v>7064326</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,6 +2220,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2246,10 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889839</v>
+        <v>125889841</v>
       </c>
       <c r="B18" t="n">
-        <v>98353</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2262,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401042</v>
+        <v>401024</v>
       </c>
       <c r="R18" t="n">
-        <v>7064326</v>
+        <v>7064328</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2317,11 +2322,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125890344</v>
       </c>
       <c r="B21" t="n">
-        <v>91922</v>
+        <v>91925</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889842</v>
+        <v>125889834</v>
       </c>
       <c r="B24" t="n">
-        <v>91585</v>
+        <v>91228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401009</v>
+        <v>401077</v>
       </c>
       <c r="R24" t="n">
-        <v>7064292</v>
+        <v>7064505</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889834</v>
+        <v>125889842</v>
       </c>
       <c r="B25" t="n">
-        <v>91228</v>
+        <v>91588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401077</v>
+        <v>401009</v>
       </c>
       <c r="R25" t="n">
-        <v>7064505</v>
+        <v>7064292</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3030,7 +3030,7 @@
         <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125889844</v>
+        <v>125890348</v>
       </c>
       <c r="B30" t="n">
-        <v>91246</v>
+        <v>98355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401002</v>
+        <v>401037</v>
       </c>
       <c r="R30" t="n">
-        <v>7064296</v>
+        <v>7064318</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,12 +3501,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3525,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889843</v>
+        <v>125889844</v>
       </c>
       <c r="B31" t="n">
         <v>91246</v>
@@ -3560,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401114</v>
+        <v>401002</v>
       </c>
       <c r="R31" t="n">
-        <v>7064640</v>
+        <v>7064296</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3622,32 +3628,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889833</v>
+        <v>125889843</v>
       </c>
       <c r="B32" t="n">
-        <v>91193</v>
+        <v>91246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3657,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401150</v>
+        <v>401114</v>
       </c>
       <c r="R32" t="n">
-        <v>7064603</v>
+        <v>7064640</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3719,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125890348</v>
+        <v>125889833</v>
       </c>
       <c r="B33" t="n">
-        <v>98353</v>
+        <v>91193</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3730,21 +3736,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3754,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401037</v>
+        <v>401150</v>
       </c>
       <c r="R33" t="n">
-        <v>7064318</v>
+        <v>7064603</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3792,18 +3798,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>91178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R34" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B35" t="n">
-        <v>91178</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R35" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125890353</v>
+        <v>125890362</v>
       </c>
       <c r="B36" t="n">
-        <v>80071</v>
+        <v>91246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401111</v>
+        <v>400981</v>
       </c>
       <c r="R36" t="n">
-        <v>7064685</v>
+        <v>7064305</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4113,32 +4113,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890365</v>
+        <v>125890342</v>
       </c>
       <c r="B37" t="n">
-        <v>75059</v>
+        <v>91193</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401081</v>
+        <v>401266</v>
       </c>
       <c r="R37" t="n">
-        <v>7064302</v>
+        <v>7064514</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890362</v>
+        <v>125890353</v>
       </c>
       <c r="B38" t="n">
-        <v>91246</v>
+        <v>80071</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4221,21 +4221,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>400981</v>
+        <v>401111</v>
       </c>
       <c r="R38" t="n">
-        <v>7064305</v>
+        <v>7064685</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890342</v>
+        <v>125890365</v>
       </c>
       <c r="B39" t="n">
-        <v>91193</v>
+        <v>75059</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401266</v>
+        <v>401081</v>
       </c>
       <c r="R39" t="n">
-        <v>7064514</v>
+        <v>7064302</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -3124,10 +3124,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125889849</v>
+        <v>125889829</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401254</v>
+        <v>401164</v>
       </c>
       <c r="R27" t="n">
-        <v>7064480</v>
+        <v>7064559</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125889829</v>
+        <v>125889849</v>
       </c>
       <c r="B28" t="n">
-        <v>75067</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401164</v>
+        <v>401254</v>
       </c>
       <c r="R28" t="n">
-        <v>7064559</v>
+        <v>7064480</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B34" t="n">
-        <v>91178</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R34" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>91178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R35" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890353</v>
+        <v>125890365</v>
       </c>
       <c r="B38" t="n">
-        <v>80071</v>
+        <v>75059</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4221,21 +4221,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401111</v>
+        <v>401081</v>
       </c>
       <c r="R38" t="n">
-        <v>7064685</v>
+        <v>7064302</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890365</v>
+        <v>125890353</v>
       </c>
       <c r="B39" t="n">
-        <v>75059</v>
+        <v>80071</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401081</v>
+        <v>401111</v>
       </c>
       <c r="R39" t="n">
-        <v>7064302</v>
+        <v>7064685</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125890366</v>
+        <v>125889850</v>
       </c>
       <c r="B3" t="n">
-        <v>75059</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401063</v>
+        <v>401064</v>
       </c>
       <c r="R3" t="n">
-        <v>7064359</v>
+        <v>7064314</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125889850</v>
+        <v>125890358</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>91250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401064</v>
+        <v>401130</v>
       </c>
       <c r="R4" t="n">
-        <v>7064314</v>
+        <v>7064629</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890358</v>
+        <v>125890366</v>
       </c>
       <c r="B5" t="n">
-        <v>91246</v>
+        <v>75059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401130</v>
+        <v>401063</v>
       </c>
       <c r="R5" t="n">
-        <v>7064629</v>
+        <v>7064359</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1182,7 +1182,7 @@
         <v>125890359</v>
       </c>
       <c r="B7" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890363</v>
+        <v>125890352</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>79131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401196</v>
+        <v>401129</v>
       </c>
       <c r="R8" t="n">
-        <v>7064572</v>
+        <v>7064590</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890357</v>
+        <v>125890351</v>
       </c>
       <c r="B9" t="n">
-        <v>91246</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401016</v>
+        <v>401128</v>
       </c>
       <c r="R9" t="n">
-        <v>7064444</v>
+        <v>7064635</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890352</v>
+        <v>125890363</v>
       </c>
       <c r="B10" t="n">
-        <v>79127</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401129</v>
+        <v>401196</v>
       </c>
       <c r="R10" t="n">
-        <v>7064590</v>
+        <v>7064572</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890351</v>
+        <v>125890357</v>
       </c>
       <c r="B11" t="n">
-        <v>80072</v>
+        <v>91250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401128</v>
+        <v>401016</v>
       </c>
       <c r="R11" t="n">
-        <v>7064635</v>
+        <v>7064444</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125890341</v>
+        <v>125889848</v>
       </c>
       <c r="B13" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401174</v>
+        <v>401108</v>
       </c>
       <c r="R13" t="n">
-        <v>7064577</v>
+        <v>7064676</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125889848</v>
+        <v>125890341</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1869,21 +1869,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>401108</v>
+        <v>401174</v>
       </c>
       <c r="R14" t="n">
-        <v>7064676</v>
+        <v>7064577</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889852</v>
+        <v>125889841</v>
       </c>
       <c r="B15" t="n">
-        <v>88637</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401144</v>
+        <v>401024</v>
       </c>
       <c r="R15" t="n">
-        <v>7064600</v>
+        <v>7064328</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889831</v>
+        <v>125889839</v>
       </c>
       <c r="B16" t="n">
-        <v>75067</v>
+        <v>98359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401096</v>
+        <v>401042</v>
       </c>
       <c r="R16" t="n">
-        <v>7064277</v>
+        <v>7064326</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2123,6 +2123,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2149,32 +2154,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889839</v>
+        <v>125889852</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>88641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401042</v>
+        <v>401144</v>
       </c>
       <c r="R17" t="n">
-        <v>7064326</v>
+        <v>7064600</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,11 +2225,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2251,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889841</v>
+        <v>125889831</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>75067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401024</v>
+        <v>401096</v>
       </c>
       <c r="R18" t="n">
-        <v>7064328</v>
+        <v>7064277</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125889847</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125890344</v>
       </c>
       <c r="B21" t="n">
-        <v>91925</v>
+        <v>91929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>125889834</v>
       </c>
       <c r="B24" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>125889842</v>
       </c>
       <c r="B25" t="n">
-        <v>91588</v>
+        <v>91592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125889829</v>
+        <v>125889849</v>
       </c>
       <c r="B27" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401164</v>
+        <v>401254</v>
       </c>
       <c r="R27" t="n">
-        <v>7064559</v>
+        <v>7064480</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125889849</v>
+        <v>125889829</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401254</v>
+        <v>401164</v>
       </c>
       <c r="R28" t="n">
-        <v>7064480</v>
+        <v>7064559</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125890348</v>
+        <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>91250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401037</v>
+        <v>401002</v>
       </c>
       <c r="R30" t="n">
-        <v>7064318</v>
+        <v>7064296</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,18 +3501,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3531,10 +3525,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889844</v>
+        <v>125889843</v>
       </c>
       <c r="B31" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3566,10 +3560,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401002</v>
+        <v>401114</v>
       </c>
       <c r="R31" t="n">
-        <v>7064296</v>
+        <v>7064640</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3628,32 +3622,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889843</v>
+        <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91246</v>
+        <v>91197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3657,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401114</v>
+        <v>401150</v>
       </c>
       <c r="R32" t="n">
-        <v>7064640</v>
+        <v>7064603</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,10 +3719,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125889833</v>
+        <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>91193</v>
+        <v>98359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,21 +3730,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3760,10 +3754,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401150</v>
+        <v>401037</v>
       </c>
       <c r="R33" t="n">
-        <v>7064603</v>
+        <v>7064318</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3798,12 +3792,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>125889851</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>125890347</v>
       </c>
       <c r="B35" t="n">
-        <v>91178</v>
+        <v>91182</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125890362</v>
+        <v>125890365</v>
       </c>
       <c r="B36" t="n">
-        <v>91246</v>
+        <v>75059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>400981</v>
+        <v>401081</v>
       </c>
       <c r="R36" t="n">
-        <v>7064305</v>
+        <v>7064302</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4113,32 +4113,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890342</v>
+        <v>125890353</v>
       </c>
       <c r="B37" t="n">
-        <v>91193</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401266</v>
+        <v>401111</v>
       </c>
       <c r="R37" t="n">
-        <v>7064514</v>
+        <v>7064685</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890365</v>
+        <v>125890362</v>
       </c>
       <c r="B38" t="n">
-        <v>75059</v>
+        <v>91250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4221,21 +4221,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401081</v>
+        <v>400981</v>
       </c>
       <c r="R38" t="n">
-        <v>7064302</v>
+        <v>7064305</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890353</v>
+        <v>125890342</v>
       </c>
       <c r="B39" t="n">
-        <v>80071</v>
+        <v>91197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401111</v>
+        <v>401266</v>
       </c>
       <c r="R39" t="n">
-        <v>7064685</v>
+        <v>7064514</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>75059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R3" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R4" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890366</v>
+        <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>75059</v>
+        <v>91250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401063</v>
+        <v>401130</v>
       </c>
       <c r="R5" t="n">
-        <v>7064359</v>
+        <v>7064629</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889834</v>
+        <v>125889837</v>
       </c>
       <c r="B24" t="n">
-        <v>91232</v>
+        <v>98359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401077</v>
+        <v>401214</v>
       </c>
       <c r="R24" t="n">
-        <v>7064505</v>
+        <v>7064364</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889842</v>
+        <v>125889834</v>
       </c>
       <c r="B25" t="n">
-        <v>91592</v>
+        <v>91232</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401009</v>
+        <v>401077</v>
       </c>
       <c r="R25" t="n">
-        <v>7064292</v>
+        <v>7064505</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889837</v>
+        <v>125889842</v>
       </c>
       <c r="B26" t="n">
-        <v>98359</v>
+        <v>91592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>2063</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401214</v>
+        <v>401009</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064292</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125890366</v>
+        <v>125889850</v>
       </c>
       <c r="B3" t="n">
-        <v>75059</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401063</v>
+        <v>401064</v>
       </c>
       <c r="R3" t="n">
-        <v>7064359</v>
+        <v>7064314</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125889850</v>
+        <v>125890358</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401064</v>
+        <v>401130</v>
       </c>
       <c r="R4" t="n">
-        <v>7064314</v>
+        <v>7064629</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890358</v>
+        <v>125890366</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>75059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401130</v>
+        <v>401063</v>
       </c>
       <c r="R5" t="n">
-        <v>7064629</v>
+        <v>7064359</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890352</v>
+        <v>125890363</v>
       </c>
       <c r="B8" t="n">
-        <v>79131</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401129</v>
+        <v>401196</v>
       </c>
       <c r="R8" t="n">
-        <v>7064590</v>
+        <v>7064572</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890351</v>
+        <v>125890357</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401128</v>
+        <v>401016</v>
       </c>
       <c r="R9" t="n">
-        <v>7064635</v>
+        <v>7064444</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890363</v>
+        <v>125890351</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401196</v>
+        <v>401128</v>
       </c>
       <c r="R10" t="n">
-        <v>7064572</v>
+        <v>7064635</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890357</v>
+        <v>125890352</v>
       </c>
       <c r="B11" t="n">
-        <v>91250</v>
+        <v>79131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401016</v>
+        <v>401129</v>
       </c>
       <c r="R11" t="n">
-        <v>7064444</v>
+        <v>7064590</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125889830</v>
+        <v>125889848</v>
       </c>
       <c r="B12" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401228</v>
+        <v>401108</v>
       </c>
       <c r="R12" t="n">
-        <v>7064385</v>
+        <v>7064676</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125889848</v>
+        <v>125889830</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>75067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401108</v>
+        <v>401228</v>
       </c>
       <c r="R13" t="n">
-        <v>7064676</v>
+        <v>7064385</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889841</v>
+        <v>125889852</v>
       </c>
       <c r="B15" t="n">
-        <v>58020</v>
+        <v>88641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401024</v>
+        <v>401144</v>
       </c>
       <c r="R15" t="n">
-        <v>7064328</v>
+        <v>7064600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889839</v>
+        <v>125889831</v>
       </c>
       <c r="B16" t="n">
-        <v>98359</v>
+        <v>75067</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401042</v>
+        <v>401096</v>
       </c>
       <c r="R16" t="n">
-        <v>7064326</v>
+        <v>7064277</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2123,11 +2123,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2154,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889852</v>
+        <v>125889841</v>
       </c>
       <c r="B17" t="n">
-        <v>88641</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401144</v>
+        <v>401024</v>
       </c>
       <c r="R17" t="n">
-        <v>7064600</v>
+        <v>7064328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2251,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889831</v>
+        <v>125889839</v>
       </c>
       <c r="B18" t="n">
-        <v>75067</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401096</v>
+        <v>401042</v>
       </c>
       <c r="R18" t="n">
-        <v>7064277</v>
+        <v>7064326</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2322,6 +2317,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889837</v>
+        <v>125889834</v>
       </c>
       <c r="B24" t="n">
-        <v>98359</v>
+        <v>91232</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401214</v>
+        <v>401077</v>
       </c>
       <c r="R24" t="n">
-        <v>7064364</v>
+        <v>7064505</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889834</v>
+        <v>125889842</v>
       </c>
       <c r="B25" t="n">
-        <v>91232</v>
+        <v>91592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401077</v>
+        <v>401009</v>
       </c>
       <c r="R25" t="n">
-        <v>7064505</v>
+        <v>7064292</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889842</v>
+        <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>91592</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2063</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401009</v>
+        <v>401214</v>
       </c>
       <c r="R26" t="n">
-        <v>7064292</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125889849</v>
+        <v>125889829</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>75067</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401254</v>
+        <v>401164</v>
       </c>
       <c r="R27" t="n">
-        <v>7064480</v>
+        <v>7064559</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125889829</v>
+        <v>125889849</v>
       </c>
       <c r="B28" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401164</v>
+        <v>401254</v>
       </c>
       <c r="R28" t="n">
-        <v>7064559</v>
+        <v>7064480</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125889844</v>
+        <v>125890348</v>
       </c>
       <c r="B30" t="n">
-        <v>91250</v>
+        <v>98360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401002</v>
+        <v>401037</v>
       </c>
       <c r="R30" t="n">
-        <v>7064296</v>
+        <v>7064318</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,12 +3501,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3525,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889843</v>
+        <v>125889844</v>
       </c>
       <c r="B31" t="n">
         <v>91250</v>
@@ -3560,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401114</v>
+        <v>401002</v>
       </c>
       <c r="R31" t="n">
-        <v>7064640</v>
+        <v>7064296</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3622,32 +3628,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889833</v>
+        <v>125889843</v>
       </c>
       <c r="B32" t="n">
-        <v>91197</v>
+        <v>91250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3657,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401150</v>
+        <v>401114</v>
       </c>
       <c r="R32" t="n">
-        <v>7064603</v>
+        <v>7064640</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3719,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125890348</v>
+        <v>125889833</v>
       </c>
       <c r="B33" t="n">
-        <v>98359</v>
+        <v>91197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3730,21 +3736,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3754,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401037</v>
+        <v>401150</v>
       </c>
       <c r="R33" t="n">
-        <v>7064318</v>
+        <v>7064603</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3792,18 +3798,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>91182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R34" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B35" t="n">
-        <v>91182</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R35" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890353</v>
+        <v>125890362</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>91250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,21 +4124,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401111</v>
+        <v>400981</v>
       </c>
       <c r="R37" t="n">
-        <v>7064685</v>
+        <v>7064305</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890362</v>
+        <v>125890342</v>
       </c>
       <c r="B38" t="n">
-        <v>91250</v>
+        <v>91197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>400981</v>
+        <v>401266</v>
       </c>
       <c r="R38" t="n">
-        <v>7064305</v>
+        <v>7064514</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890342</v>
+        <v>125890353</v>
       </c>
       <c r="B39" t="n">
-        <v>91197</v>
+        <v>80075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401266</v>
+        <v>401111</v>
       </c>
       <c r="R39" t="n">
-        <v>7064514</v>
+        <v>7064685</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>75059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R3" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R4" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890366</v>
+        <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>75059</v>
+        <v>91250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401063</v>
+        <v>401130</v>
       </c>
       <c r="R5" t="n">
-        <v>7064359</v>
+        <v>7064629</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B15" t="n">
-        <v>88641</v>
+        <v>75067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R15" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889831</v>
+        <v>125889839</v>
       </c>
       <c r="B16" t="n">
-        <v>75067</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401096</v>
+        <v>401042</v>
       </c>
       <c r="R16" t="n">
-        <v>7064277</v>
+        <v>7064326</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2123,6 +2123,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2246,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889839</v>
+        <v>125889852</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>88641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401042</v>
+        <v>401144</v>
       </c>
       <c r="R18" t="n">
-        <v>7064326</v>
+        <v>7064600</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2317,11 +2322,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125890366</v>
+        <v>125889850</v>
       </c>
       <c r="B3" t="n">
-        <v>75059</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401063</v>
+        <v>401064</v>
       </c>
       <c r="R3" t="n">
-        <v>7064359</v>
+        <v>7064314</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125889850</v>
+        <v>125890358</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401064</v>
+        <v>401130</v>
       </c>
       <c r="R4" t="n">
-        <v>7064314</v>
+        <v>7064629</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890358</v>
+        <v>125890366</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>75059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401130</v>
+        <v>401063</v>
       </c>
       <c r="R5" t="n">
-        <v>7064629</v>
+        <v>7064359</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890363</v>
+        <v>125890352</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>79131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401196</v>
+        <v>401129</v>
       </c>
       <c r="R8" t="n">
-        <v>7064572</v>
+        <v>7064590</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890357</v>
+        <v>125890363</v>
       </c>
       <c r="B9" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401016</v>
+        <v>401196</v>
       </c>
       <c r="R9" t="n">
-        <v>7064444</v>
+        <v>7064572</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890351</v>
+        <v>125890357</v>
       </c>
       <c r="B10" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401128</v>
+        <v>401016</v>
       </c>
       <c r="R10" t="n">
-        <v>7064635</v>
+        <v>7064444</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890352</v>
+        <v>125890351</v>
       </c>
       <c r="B11" t="n">
-        <v>79131</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401129</v>
+        <v>401128</v>
       </c>
       <c r="R11" t="n">
-        <v>7064590</v>
+        <v>7064635</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125889829</v>
+        <v>125889849</v>
       </c>
       <c r="B27" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,21 +3135,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401164</v>
+        <v>401254</v>
       </c>
       <c r="R27" t="n">
-        <v>7064559</v>
+        <v>7064480</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125889849</v>
+        <v>125889829</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>75067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401254</v>
+        <v>401164</v>
       </c>
       <c r="R28" t="n">
-        <v>7064480</v>
+        <v>7064559</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125890348</v>
+        <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>98360</v>
+        <v>91250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401037</v>
+        <v>401002</v>
       </c>
       <c r="R30" t="n">
-        <v>7064318</v>
+        <v>7064296</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,18 +3501,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3531,7 +3525,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889844</v>
+        <v>125889843</v>
       </c>
       <c r="B31" t="n">
         <v>91250</v>
@@ -3566,10 +3560,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401002</v>
+        <v>401114</v>
       </c>
       <c r="R31" t="n">
-        <v>7064296</v>
+        <v>7064640</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3628,32 +3622,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889843</v>
+        <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91250</v>
+        <v>91197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3657,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401114</v>
+        <v>401150</v>
       </c>
       <c r="R32" t="n">
-        <v>7064640</v>
+        <v>7064603</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,10 +3719,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125889833</v>
+        <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>91197</v>
+        <v>98360</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,21 +3730,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3760,10 +3754,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401150</v>
+        <v>401037</v>
       </c>
       <c r="R33" t="n">
-        <v>7064603</v>
+        <v>7064318</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3798,12 +3792,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>75060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R3" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>91250</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R4" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890366</v>
+        <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>75059</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401063</v>
+        <v>401130</v>
       </c>
       <c r="R5" t="n">
-        <v>7064359</v>
+        <v>7064629</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,7 +1085,7 @@
         <v>125889832</v>
       </c>
       <c r="B6" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>125890359</v>
       </c>
       <c r="B7" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>125890352</v>
       </c>
       <c r="B8" t="n">
-        <v>79131</v>
+        <v>79132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>125890363</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>125890357</v>
       </c>
       <c r="B10" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>125890351</v>
       </c>
       <c r="B11" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125889848</v>
+        <v>125889830</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>75068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401108</v>
+        <v>401228</v>
       </c>
       <c r="R12" t="n">
-        <v>7064676</v>
+        <v>7064385</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125889830</v>
+        <v>125889848</v>
       </c>
       <c r="B13" t="n">
-        <v>75067</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401228</v>
+        <v>401108</v>
       </c>
       <c r="R13" t="n">
-        <v>7064385</v>
+        <v>7064676</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1861,7 +1861,7 @@
         <v>125890341</v>
       </c>
       <c r="B14" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889831</v>
+        <v>125889841</v>
       </c>
       <c r="B15" t="n">
-        <v>75067</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401096</v>
+        <v>401024</v>
       </c>
       <c r="R15" t="n">
-        <v>7064277</v>
+        <v>7064328</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2055,7 +2055,7 @@
         <v>125889839</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,32 +2154,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889841</v>
+        <v>125889852</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>88643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401024</v>
+        <v>401144</v>
       </c>
       <c r="R17" t="n">
-        <v>7064328</v>
+        <v>7064600</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B18" t="n">
-        <v>88641</v>
+        <v>75068</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,21 +2262,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R18" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125889847</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125890344</v>
       </c>
       <c r="B21" t="n">
-        <v>91929</v>
+        <v>91931</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889834</v>
+        <v>125889842</v>
       </c>
       <c r="B24" t="n">
-        <v>91232</v>
+        <v>91594</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401077</v>
+        <v>401009</v>
       </c>
       <c r="R24" t="n">
-        <v>7064505</v>
+        <v>7064292</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889842</v>
+        <v>125889837</v>
       </c>
       <c r="B25" t="n">
-        <v>91592</v>
+        <v>98362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2063</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401009</v>
+        <v>401214</v>
       </c>
       <c r="R25" t="n">
-        <v>7064292</v>
+        <v>7064364</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889837</v>
+        <v>125889834</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>91234</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401214</v>
+        <v>401077</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064505</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3127,7 +3127,7 @@
         <v>125889849</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>125889829</v>
       </c>
       <c r="B28" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>125890345</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>125889843</v>
       </c>
       <c r="B31" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B34" t="n">
-        <v>91182</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R34" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>91184</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R35" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4019,7 +4019,7 @@
         <v>125890365</v>
       </c>
       <c r="B36" t="n">
-        <v>75059</v>
+        <v>75060</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>125890362</v>
       </c>
       <c r="B37" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>125890342</v>
       </c>
       <c r="B38" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>125890353</v>
       </c>
       <c r="B39" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889841</v>
+        <v>125889852</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>88643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401024</v>
+        <v>401144</v>
       </c>
       <c r="R15" t="n">
-        <v>7064328</v>
+        <v>7064600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889839</v>
+        <v>125889831</v>
       </c>
       <c r="B16" t="n">
-        <v>98362</v>
+        <v>75068</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401042</v>
+        <v>401096</v>
       </c>
       <c r="R16" t="n">
-        <v>7064326</v>
+        <v>7064277</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2123,11 +2123,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2154,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889852</v>
+        <v>125889839</v>
       </c>
       <c r="B17" t="n">
-        <v>88643</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401144</v>
+        <v>401042</v>
       </c>
       <c r="R17" t="n">
-        <v>7064600</v>
+        <v>7064326</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2225,6 +2220,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2251,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889831</v>
+        <v>125889841</v>
       </c>
       <c r="B18" t="n">
-        <v>75068</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401096</v>
+        <v>401024</v>
       </c>
       <c r="R18" t="n">
-        <v>7064277</v>
+        <v>7064328</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889842</v>
+        <v>125889834</v>
       </c>
       <c r="B24" t="n">
-        <v>91594</v>
+        <v>91234</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401009</v>
+        <v>401077</v>
       </c>
       <c r="R24" t="n">
-        <v>7064292</v>
+        <v>7064505</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889837</v>
+        <v>125889842</v>
       </c>
       <c r="B25" t="n">
-        <v>98362</v>
+        <v>91594</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>2063</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401214</v>
+        <v>401009</v>
       </c>
       <c r="R25" t="n">
-        <v>7064364</v>
+        <v>7064292</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889834</v>
+        <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>91234</v>
+        <v>98362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401077</v>
+        <v>401214</v>
       </c>
       <c r="R26" t="n">
-        <v>7064505</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125889850</v>
+        <v>125890358</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401064</v>
+        <v>401130</v>
       </c>
       <c r="R4" t="n">
-        <v>7064314</v>
+        <v>7064629</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R5" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1182,7 +1182,7 @@
         <v>125890359</v>
       </c>
       <c r="B7" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890352</v>
+        <v>125890363</v>
       </c>
       <c r="B8" t="n">
-        <v>79132</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401129</v>
+        <v>401196</v>
       </c>
       <c r="R8" t="n">
-        <v>7064590</v>
+        <v>7064572</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890363</v>
+        <v>125890357</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401196</v>
+        <v>401016</v>
       </c>
       <c r="R9" t="n">
-        <v>7064572</v>
+        <v>7064444</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890357</v>
+        <v>125890351</v>
       </c>
       <c r="B10" t="n">
-        <v>91252</v>
+        <v>80077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401016</v>
+        <v>401128</v>
       </c>
       <c r="R10" t="n">
-        <v>7064444</v>
+        <v>7064635</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890351</v>
+        <v>125890352</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>79132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401128</v>
+        <v>401129</v>
       </c>
       <c r="R11" t="n">
-        <v>7064635</v>
+        <v>7064590</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1958,7 +1958,7 @@
         <v>125889852</v>
       </c>
       <c r="B15" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889831</v>
+        <v>125889839</v>
       </c>
       <c r="B16" t="n">
-        <v>75068</v>
+        <v>98364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401096</v>
+        <v>401042</v>
       </c>
       <c r="R16" t="n">
-        <v>7064277</v>
+        <v>7064326</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2123,6 +2123,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2149,32 +2154,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889839</v>
+        <v>125889831</v>
       </c>
       <c r="B17" t="n">
-        <v>98362</v>
+        <v>75068</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401042</v>
+        <v>401096</v>
       </c>
       <c r="R17" t="n">
-        <v>7064326</v>
+        <v>7064277</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,11 +2225,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125890344</v>
       </c>
       <c r="B21" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889834</v>
+        <v>125889842</v>
       </c>
       <c r="B24" t="n">
-        <v>91234</v>
+        <v>91596</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401077</v>
+        <v>401009</v>
       </c>
       <c r="R24" t="n">
-        <v>7064505</v>
+        <v>7064292</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889842</v>
+        <v>125889834</v>
       </c>
       <c r="B25" t="n">
-        <v>91594</v>
+        <v>91236</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401009</v>
+        <v>401077</v>
       </c>
       <c r="R25" t="n">
-        <v>7064292</v>
+        <v>7064505</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3030,7 +3030,7 @@
         <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>125889843</v>
       </c>
       <c r="B31" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>91186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R34" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B35" t="n">
-        <v>91184</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R35" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890362</v>
+        <v>125890353</v>
       </c>
       <c r="B37" t="n">
-        <v>91252</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,21 +4124,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>400981</v>
+        <v>401111</v>
       </c>
       <c r="R37" t="n">
-        <v>7064305</v>
+        <v>7064685</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890342</v>
+        <v>125890362</v>
       </c>
       <c r="B38" t="n">
-        <v>91199</v>
+        <v>91254</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401266</v>
+        <v>400981</v>
       </c>
       <c r="R38" t="n">
-        <v>7064514</v>
+        <v>7064305</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890353</v>
+        <v>125890342</v>
       </c>
       <c r="B39" t="n">
-        <v>80076</v>
+        <v>91201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401111</v>
+        <v>401266</v>
       </c>
       <c r="R39" t="n">
-        <v>7064685</v>
+        <v>7064514</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>91254</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R4" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125889850</v>
+        <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401064</v>
+        <v>401130</v>
       </c>
       <c r="R5" t="n">
-        <v>7064314</v>
+        <v>7064629</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B15" t="n">
-        <v>88645</v>
+        <v>75068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R15" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889839</v>
+        <v>125889852</v>
       </c>
       <c r="B16" t="n">
-        <v>98364</v>
+        <v>88645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401042</v>
+        <v>401144</v>
       </c>
       <c r="R16" t="n">
-        <v>7064326</v>
+        <v>7064600</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2123,11 +2123,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2154,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889831</v>
+        <v>125889841</v>
       </c>
       <c r="B17" t="n">
-        <v>75068</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401096</v>
+        <v>401024</v>
       </c>
       <c r="R17" t="n">
-        <v>7064277</v>
+        <v>7064328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2251,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889841</v>
+        <v>125889839</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>98364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401024</v>
+        <v>401042</v>
       </c>
       <c r="R18" t="n">
-        <v>7064328</v>
+        <v>7064326</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2322,6 +2317,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -988,7 +988,7 @@
         <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>125890359</v>
       </c>
       <c r="B7" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890363</v>
+        <v>125890352</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>79132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401196</v>
+        <v>401129</v>
       </c>
       <c r="R8" t="n">
-        <v>7064572</v>
+        <v>7064590</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890357</v>
+        <v>125890351</v>
       </c>
       <c r="B9" t="n">
-        <v>91254</v>
+        <v>80077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401016</v>
+        <v>401128</v>
       </c>
       <c r="R9" t="n">
-        <v>7064444</v>
+        <v>7064635</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890351</v>
+        <v>125890363</v>
       </c>
       <c r="B10" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401128</v>
+        <v>401196</v>
       </c>
       <c r="R10" t="n">
-        <v>7064635</v>
+        <v>7064572</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890352</v>
+        <v>125890357</v>
       </c>
       <c r="B11" t="n">
-        <v>79132</v>
+        <v>91256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401129</v>
+        <v>401016</v>
       </c>
       <c r="R11" t="n">
-        <v>7064590</v>
+        <v>7064444</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889831</v>
+        <v>125889852</v>
       </c>
       <c r="B15" t="n">
-        <v>75068</v>
+        <v>88647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401096</v>
+        <v>401144</v>
       </c>
       <c r="R15" t="n">
-        <v>7064277</v>
+        <v>7064600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B16" t="n">
-        <v>88645</v>
+        <v>75068</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R16" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889841</v>
+        <v>125889839</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>98366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401024</v>
+        <v>401042</v>
       </c>
       <c r="R17" t="n">
-        <v>7064328</v>
+        <v>7064326</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,6 +2220,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2246,10 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889839</v>
+        <v>125889841</v>
       </c>
       <c r="B18" t="n">
-        <v>98364</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2262,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401042</v>
+        <v>401024</v>
       </c>
       <c r="R18" t="n">
-        <v>7064326</v>
+        <v>7064328</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2317,11 +2322,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,32 +2445,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125889847</v>
+        <v>125890344</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>91935</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401042</v>
+        <v>401026</v>
       </c>
       <c r="R20" t="n">
         <v>7064458</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125890344</v>
+        <v>125889847</v>
       </c>
       <c r="B21" t="n">
-        <v>91933</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401026</v>
+        <v>401042</v>
       </c>
       <c r="R21" t="n">
         <v>7064458</v>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889842</v>
+        <v>125889837</v>
       </c>
       <c r="B24" t="n">
-        <v>91596</v>
+        <v>98366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2063</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401009</v>
+        <v>401214</v>
       </c>
       <c r="R24" t="n">
-        <v>7064292</v>
+        <v>7064364</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2933,7 +2933,7 @@
         <v>125889834</v>
       </c>
       <c r="B25" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889837</v>
+        <v>125889842</v>
       </c>
       <c r="B26" t="n">
-        <v>98364</v>
+        <v>91598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>2063</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401214</v>
+        <v>401009</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064292</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125889844</v>
+        <v>125890348</v>
       </c>
       <c r="B30" t="n">
-        <v>91254</v>
+        <v>98366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401002</v>
+        <v>401037</v>
       </c>
       <c r="R30" t="n">
-        <v>7064296</v>
+        <v>7064318</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,12 +3501,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3525,10 +3531,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889843</v>
+        <v>125889844</v>
       </c>
       <c r="B31" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3560,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401114</v>
+        <v>401002</v>
       </c>
       <c r="R31" t="n">
-        <v>7064640</v>
+        <v>7064296</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3622,32 +3628,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889833</v>
+        <v>125889843</v>
       </c>
       <c r="B32" t="n">
-        <v>91201</v>
+        <v>91256</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3657,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401150</v>
+        <v>401114</v>
       </c>
       <c r="R32" t="n">
-        <v>7064603</v>
+        <v>7064640</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3719,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125890348</v>
+        <v>125889833</v>
       </c>
       <c r="B33" t="n">
-        <v>98364</v>
+        <v>91203</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3730,21 +3736,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3754,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401037</v>
+        <v>401150</v>
       </c>
       <c r="R33" t="n">
-        <v>7064318</v>
+        <v>7064603</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3792,18 +3798,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B34" t="n">
-        <v>91186</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R34" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>91188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R35" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125890365</v>
+        <v>125890353</v>
       </c>
       <c r="B36" t="n">
-        <v>75060</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401081</v>
+        <v>401111</v>
       </c>
       <c r="R36" t="n">
-        <v>7064302</v>
+        <v>7064685</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890353</v>
+        <v>125890362</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>91256</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,21 +4124,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401111</v>
+        <v>400981</v>
       </c>
       <c r="R37" t="n">
-        <v>7064685</v>
+        <v>7064305</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890362</v>
+        <v>125890342</v>
       </c>
       <c r="B38" t="n">
-        <v>91254</v>
+        <v>91203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>400981</v>
+        <v>401266</v>
       </c>
       <c r="R38" t="n">
-        <v>7064305</v>
+        <v>7064514</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890342</v>
+        <v>125890365</v>
       </c>
       <c r="B39" t="n">
-        <v>91201</v>
+        <v>75060</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401266</v>
+        <v>401081</v>
       </c>
       <c r="R39" t="n">
-        <v>7064514</v>
+        <v>7064302</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889839</v>
+        <v>125889841</v>
       </c>
       <c r="B17" t="n">
-        <v>98366</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401042</v>
+        <v>401024</v>
       </c>
       <c r="R17" t="n">
-        <v>7064326</v>
+        <v>7064328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,11 +2220,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2251,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889841</v>
+        <v>125889839</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>98366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401024</v>
+        <v>401042</v>
       </c>
       <c r="R18" t="n">
-        <v>7064328</v>
+        <v>7064326</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2322,6 +2317,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889837</v>
+        <v>125889842</v>
       </c>
       <c r="B24" t="n">
-        <v>98366</v>
+        <v>91598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>2063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401214</v>
+        <v>401009</v>
       </c>
       <c r="R24" t="n">
-        <v>7064364</v>
+        <v>7064292</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889842</v>
+        <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>91598</v>
+        <v>98366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2063</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401009</v>
+        <v>401214</v>
       </c>
       <c r="R26" t="n">
-        <v>7064292</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125890366</v>
+        <v>125890358</v>
       </c>
       <c r="B3" t="n">
-        <v>75060</v>
+        <v>91260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401063</v>
+        <v>401130</v>
       </c>
       <c r="R3" t="n">
-        <v>7064359</v>
+        <v>7064629</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>75064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R4" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R5" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,7 +1085,7 @@
         <v>125889832</v>
       </c>
       <c r="B6" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>125890359</v>
       </c>
       <c r="B7" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>125890352</v>
       </c>
       <c r="B8" t="n">
-        <v>79132</v>
+        <v>79136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890351</v>
+        <v>125890357</v>
       </c>
       <c r="B9" t="n">
-        <v>80077</v>
+        <v>91260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401128</v>
+        <v>401016</v>
       </c>
       <c r="R9" t="n">
-        <v>7064635</v>
+        <v>7064444</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890363</v>
+        <v>125890351</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>80081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401196</v>
+        <v>401128</v>
       </c>
       <c r="R10" t="n">
-        <v>7064572</v>
+        <v>7064635</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890357</v>
+        <v>125890363</v>
       </c>
       <c r="B11" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401016</v>
+        <v>401196</v>
       </c>
       <c r="R11" t="n">
-        <v>7064444</v>
+        <v>7064572</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1667,7 +1667,7 @@
         <v>125889830</v>
       </c>
       <c r="B12" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>125889848</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>125890341</v>
       </c>
       <c r="B14" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B15" t="n">
-        <v>88647</v>
+        <v>75072</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R15" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889831</v>
+        <v>125889841</v>
       </c>
       <c r="B16" t="n">
-        <v>75068</v>
+        <v>58025</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401096</v>
+        <v>401024</v>
       </c>
       <c r="R16" t="n">
-        <v>7064277</v>
+        <v>7064328</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889841</v>
+        <v>125889839</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>98370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401024</v>
+        <v>401042</v>
       </c>
       <c r="R17" t="n">
-        <v>7064328</v>
+        <v>7064326</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,6 +2220,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2246,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889839</v>
+        <v>125889852</v>
       </c>
       <c r="B18" t="n">
-        <v>98366</v>
+        <v>88651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401042</v>
+        <v>401144</v>
       </c>
       <c r="R18" t="n">
-        <v>7064326</v>
+        <v>7064600</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2317,11 +2322,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125890344</v>
       </c>
       <c r="B20" t="n">
-        <v>91935</v>
+        <v>91939</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125889847</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889842</v>
+        <v>125889834</v>
       </c>
       <c r="B24" t="n">
-        <v>91598</v>
+        <v>91242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401009</v>
+        <v>401077</v>
       </c>
       <c r="R24" t="n">
-        <v>7064292</v>
+        <v>7064505</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889834</v>
+        <v>125889842</v>
       </c>
       <c r="B25" t="n">
-        <v>91238</v>
+        <v>91602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401077</v>
+        <v>401009</v>
       </c>
       <c r="R25" t="n">
-        <v>7064505</v>
+        <v>7064292</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3030,7 +3030,7 @@
         <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>125889849</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>125889829</v>
       </c>
       <c r="B28" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>125890345</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125890348</v>
+        <v>125889833</v>
       </c>
       <c r="B30" t="n">
-        <v>98366</v>
+        <v>91207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3439,21 +3439,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401037</v>
+        <v>401150</v>
       </c>
       <c r="R30" t="n">
-        <v>7064318</v>
+        <v>7064603</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,18 +3501,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3534,7 +3528,7 @@
         <v>125889844</v>
       </c>
       <c r="B31" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,7 +3625,7 @@
         <v>125889843</v>
       </c>
       <c r="B32" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3725,10 +3719,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125889833</v>
+        <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>91203</v>
+        <v>98370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,21 +3730,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3760,10 +3754,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401150</v>
+        <v>401037</v>
       </c>
       <c r="R33" t="n">
-        <v>7064603</v>
+        <v>7064318</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3798,12 +3792,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125889851</v>
+        <v>125890347</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>91192</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401035</v>
+        <v>401276</v>
       </c>
       <c r="R34" t="n">
-        <v>7064310</v>
+        <v>7064509</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125890347</v>
+        <v>125889851</v>
       </c>
       <c r="B35" t="n">
-        <v>91188</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3930,21 +3930,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401276</v>
+        <v>401035</v>
       </c>
       <c r="R35" t="n">
-        <v>7064509</v>
+        <v>7064310</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125890353</v>
+        <v>125890365</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>75064</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401111</v>
+        <v>401081</v>
       </c>
       <c r="R36" t="n">
-        <v>7064685</v>
+        <v>7064302</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4116,7 +4116,7 @@
         <v>125890362</v>
       </c>
       <c r="B37" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890342</v>
+        <v>125890353</v>
       </c>
       <c r="B38" t="n">
-        <v>91203</v>
+        <v>80080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401266</v>
+        <v>401111</v>
       </c>
       <c r="R38" t="n">
-        <v>7064514</v>
+        <v>7064685</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890365</v>
+        <v>125890342</v>
       </c>
       <c r="B39" t="n">
-        <v>75060</v>
+        <v>91207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401081</v>
+        <v>401266</v>
       </c>
       <c r="R39" t="n">
-        <v>7064302</v>
+        <v>7064514</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125890366</v>
+        <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>75064</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401063</v>
+        <v>401064</v>
       </c>
       <c r="R4" t="n">
-        <v>7064359</v>
+        <v>7064314</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>75064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R5" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889831</v>
+        <v>125889852</v>
       </c>
       <c r="B15" t="n">
-        <v>75072</v>
+        <v>88651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401096</v>
+        <v>401144</v>
       </c>
       <c r="R15" t="n">
-        <v>7064277</v>
+        <v>7064600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889841</v>
+        <v>125889831</v>
       </c>
       <c r="B16" t="n">
-        <v>58025</v>
+        <v>75072</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401024</v>
+        <v>401096</v>
       </c>
       <c r="R16" t="n">
-        <v>7064328</v>
+        <v>7064277</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889839</v>
+        <v>125889841</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>58025</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401042</v>
+        <v>401024</v>
       </c>
       <c r="R17" t="n">
-        <v>7064326</v>
+        <v>7064328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,11 +2220,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2251,32 +2246,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889852</v>
+        <v>125889839</v>
       </c>
       <c r="B18" t="n">
-        <v>88651</v>
+        <v>98370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401144</v>
+        <v>401042</v>
       </c>
       <c r="R18" t="n">
-        <v>7064600</v>
+        <v>7064326</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2322,6 +2317,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B3" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R3" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125889850</v>
+        <v>125890358</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401064</v>
+        <v>401130</v>
       </c>
       <c r="R4" t="n">
-        <v>7064314</v>
+        <v>7064629</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890352</v>
+        <v>125890363</v>
       </c>
       <c r="B8" t="n">
-        <v>79136</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401129</v>
+        <v>401196</v>
       </c>
       <c r="R8" t="n">
-        <v>7064590</v>
+        <v>7064572</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890351</v>
+        <v>125890352</v>
       </c>
       <c r="B10" t="n">
-        <v>80081</v>
+        <v>79136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401128</v>
+        <v>401129</v>
       </c>
       <c r="R10" t="n">
-        <v>7064635</v>
+        <v>7064590</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890363</v>
+        <v>125890351</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401196</v>
+        <v>401128</v>
       </c>
       <c r="R11" t="n">
-        <v>7064572</v>
+        <v>7064635</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B15" t="n">
-        <v>88651</v>
+        <v>75072</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R15" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889831</v>
+        <v>125889839</v>
       </c>
       <c r="B16" t="n">
-        <v>75072</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401096</v>
+        <v>401042</v>
       </c>
       <c r="R16" t="n">
-        <v>7064277</v>
+        <v>7064326</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2123,6 +2123,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2149,32 +2154,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889841</v>
+        <v>125889852</v>
       </c>
       <c r="B17" t="n">
-        <v>58025</v>
+        <v>88651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401024</v>
+        <v>401144</v>
       </c>
       <c r="R17" t="n">
-        <v>7064328</v>
+        <v>7064600</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2246,10 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889839</v>
+        <v>125889841</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>58025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2262,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401042</v>
+        <v>401024</v>
       </c>
       <c r="R18" t="n">
-        <v>7064326</v>
+        <v>7064328</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2317,11 +2322,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,32 +2445,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125890344</v>
+        <v>125889847</v>
       </c>
       <c r="B20" t="n">
-        <v>91939</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401026</v>
+        <v>401042</v>
       </c>
       <c r="R20" t="n">
         <v>7064458</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125889847</v>
+        <v>125890344</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>91939</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401042</v>
+        <v>401026</v>
       </c>
       <c r="R21" t="n">
         <v>7064458</v>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125889833</v>
+        <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>91207</v>
+        <v>91260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401150</v>
+        <v>401002</v>
       </c>
       <c r="R30" t="n">
-        <v>7064603</v>
+        <v>7064296</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889844</v>
+        <v>125889843</v>
       </c>
       <c r="B31" t="n">
         <v>91260</v>
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401002</v>
+        <v>401114</v>
       </c>
       <c r="R31" t="n">
-        <v>7064296</v>
+        <v>7064640</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3622,32 +3622,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889843</v>
+        <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91260</v>
+        <v>91207</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401114</v>
+        <v>401150</v>
       </c>
       <c r="R32" t="n">
-        <v>7064640</v>
+        <v>7064603</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3722,7 +3722,7 @@
         <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125890365</v>
+        <v>125890353</v>
       </c>
       <c r="B36" t="n">
-        <v>75064</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401081</v>
+        <v>401111</v>
       </c>
       <c r="R36" t="n">
-        <v>7064302</v>
+        <v>7064685</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890353</v>
+        <v>125890342</v>
       </c>
       <c r="B38" t="n">
-        <v>80080</v>
+        <v>91207</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401111</v>
+        <v>401266</v>
       </c>
       <c r="R38" t="n">
-        <v>7064685</v>
+        <v>7064514</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890342</v>
+        <v>125890365</v>
       </c>
       <c r="B39" t="n">
-        <v>91207</v>
+        <v>75064</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401266</v>
+        <v>401081</v>
       </c>
       <c r="R39" t="n">
-        <v>7064514</v>
+        <v>7064302</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889831</v>
+        <v>125889839</v>
       </c>
       <c r="B15" t="n">
-        <v>75072</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401096</v>
+        <v>401042</v>
       </c>
       <c r="R15" t="n">
-        <v>7064277</v>
+        <v>7064326</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2026,6 +2026,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2052,32 +2057,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889839</v>
+        <v>125889831</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>75072</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2092,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401042</v>
+        <v>401096</v>
       </c>
       <c r="R16" t="n">
-        <v>7064326</v>
+        <v>7064277</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2123,11 +2128,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890363</v>
+        <v>125890351</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401196</v>
+        <v>401128</v>
       </c>
       <c r="R8" t="n">
-        <v>7064572</v>
+        <v>7064635</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890357</v>
+        <v>125890363</v>
       </c>
       <c r="B9" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401016</v>
+        <v>401196</v>
       </c>
       <c r="R9" t="n">
-        <v>7064444</v>
+        <v>7064572</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,32 +1470,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890352</v>
+        <v>125890357</v>
       </c>
       <c r="B10" t="n">
-        <v>79136</v>
+        <v>91260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401129</v>
+        <v>401016</v>
       </c>
       <c r="R10" t="n">
-        <v>7064590</v>
+        <v>7064444</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890351</v>
+        <v>125890352</v>
       </c>
       <c r="B11" t="n">
-        <v>80081</v>
+        <v>79136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401128</v>
+        <v>401129</v>
       </c>
       <c r="R11" t="n">
-        <v>7064635</v>
+        <v>7064590</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889839</v>
+        <v>125889852</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>88651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401042</v>
+        <v>401144</v>
       </c>
       <c r="R15" t="n">
-        <v>7064326</v>
+        <v>7064600</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2026,11 +2026,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889852</v>
+        <v>125889841</v>
       </c>
       <c r="B17" t="n">
-        <v>88651</v>
+        <v>58025</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401144</v>
+        <v>401024</v>
       </c>
       <c r="R17" t="n">
-        <v>7064600</v>
+        <v>7064328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2251,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889841</v>
+        <v>125889839</v>
       </c>
       <c r="B18" t="n">
-        <v>58025</v>
+        <v>98373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401024</v>
+        <v>401042</v>
       </c>
       <c r="R18" t="n">
-        <v>7064328</v>
+        <v>7064326</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2322,6 +2317,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4113,10 +4113,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890362</v>
+        <v>125890365</v>
       </c>
       <c r="B37" t="n">
-        <v>91260</v>
+        <v>75064</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,21 +4124,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>400981</v>
+        <v>401081</v>
       </c>
       <c r="R37" t="n">
-        <v>7064305</v>
+        <v>7064302</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890342</v>
+        <v>125890362</v>
       </c>
       <c r="B38" t="n">
-        <v>91207</v>
+        <v>91260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401266</v>
+        <v>400981</v>
       </c>
       <c r="R38" t="n">
-        <v>7064514</v>
+        <v>7064305</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890365</v>
+        <v>125890342</v>
       </c>
       <c r="B39" t="n">
-        <v>75064</v>
+        <v>91207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401081</v>
+        <v>401266</v>
       </c>
       <c r="R39" t="n">
-        <v>7064302</v>
+        <v>7064514</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>75064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R3" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R4" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890366</v>
+        <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>75064</v>
+        <v>91260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401063</v>
+        <v>401130</v>
       </c>
       <c r="R5" t="n">
-        <v>7064359</v>
+        <v>7064629</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125890366</v>
+        <v>125889850</v>
       </c>
       <c r="B3" t="n">
-        <v>75064</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401063</v>
+        <v>401064</v>
       </c>
       <c r="R3" t="n">
-        <v>7064359</v>
+        <v>7064314</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125889850</v>
+        <v>125890358</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401064</v>
+        <v>401130</v>
       </c>
       <c r="R4" t="n">
-        <v>7064314</v>
+        <v>7064629</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890358</v>
+        <v>125890366</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>75067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401130</v>
+        <v>401063</v>
       </c>
       <c r="R5" t="n">
-        <v>7064629</v>
+        <v>7064359</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,7 +1085,7 @@
         <v>125889832</v>
       </c>
       <c r="B6" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>125890359</v>
       </c>
       <c r="B7" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>125890351</v>
       </c>
       <c r="B8" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,32 +1373,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890363</v>
+        <v>125890352</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>79139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401196</v>
+        <v>401129</v>
       </c>
       <c r="R9" t="n">
-        <v>7064572</v>
+        <v>7064590</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890357</v>
+        <v>125890363</v>
       </c>
       <c r="B10" t="n">
-        <v>91260</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401016</v>
+        <v>401196</v>
       </c>
       <c r="R10" t="n">
-        <v>7064444</v>
+        <v>7064572</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890352</v>
+        <v>125890357</v>
       </c>
       <c r="B11" t="n">
-        <v>79136</v>
+        <v>91263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401129</v>
+        <v>401016</v>
       </c>
       <c r="R11" t="n">
-        <v>7064590</v>
+        <v>7064444</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1667,7 +1667,7 @@
         <v>125889830</v>
       </c>
       <c r="B12" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>125889848</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>125890341</v>
       </c>
       <c r="B14" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889852</v>
+        <v>125889831</v>
       </c>
       <c r="B15" t="n">
-        <v>88651</v>
+        <v>75075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401144</v>
+        <v>401096</v>
       </c>
       <c r="R15" t="n">
-        <v>7064600</v>
+        <v>7064277</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889831</v>
+        <v>125889841</v>
       </c>
       <c r="B16" t="n">
-        <v>75072</v>
+        <v>58027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401096</v>
+        <v>401024</v>
       </c>
       <c r="R16" t="n">
-        <v>7064277</v>
+        <v>7064328</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889841</v>
+        <v>125889852</v>
       </c>
       <c r="B17" t="n">
-        <v>58025</v>
+        <v>88654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401024</v>
+        <v>401144</v>
       </c>
       <c r="R17" t="n">
-        <v>7064328</v>
+        <v>7064600</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2249,7 +2249,7 @@
         <v>125889839</v>
       </c>
       <c r="B18" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>125889836</v>
       </c>
       <c r="B19" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>125889847</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125890344</v>
       </c>
       <c r="B21" t="n">
-        <v>91939</v>
+        <v>91942</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>125890350</v>
       </c>
       <c r="B22" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>125889838</v>
       </c>
       <c r="B23" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889834</v>
+        <v>125889837</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>98382</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401077</v>
+        <v>401214</v>
       </c>
       <c r="R24" t="n">
-        <v>7064505</v>
+        <v>7064364</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2933,7 +2933,7 @@
         <v>125889842</v>
       </c>
       <c r="B25" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889837</v>
+        <v>125889834</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>91245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401214</v>
+        <v>401077</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064505</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3127,7 +3127,7 @@
         <v>125889849</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>125889829</v>
       </c>
       <c r="B28" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>125890345</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>125889843</v>
       </c>
       <c r="B31" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>125890347</v>
       </c>
       <c r="B34" t="n">
-        <v>91192</v>
+        <v>91195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>125889851</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>125890353</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125890365</v>
+        <v>125890362</v>
       </c>
       <c r="B37" t="n">
-        <v>75064</v>
+        <v>91263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4124,21 +4124,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401081</v>
+        <v>400981</v>
       </c>
       <c r="R37" t="n">
-        <v>7064302</v>
+        <v>7064305</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125890362</v>
+        <v>125890342</v>
       </c>
       <c r="B38" t="n">
-        <v>91260</v>
+        <v>91210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>400981</v>
+        <v>401266</v>
       </c>
       <c r="R38" t="n">
-        <v>7064305</v>
+        <v>7064514</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890342</v>
+        <v>125890365</v>
       </c>
       <c r="B39" t="n">
-        <v>91207</v>
+        <v>75067</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401266</v>
+        <v>401081</v>
       </c>
       <c r="R39" t="n">
-        <v>7064514</v>
+        <v>7064302</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889841</v>
+        <v>125889852</v>
       </c>
       <c r="B16" t="n">
-        <v>58027</v>
+        <v>88654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401024</v>
+        <v>401144</v>
       </c>
       <c r="R16" t="n">
-        <v>7064328</v>
+        <v>7064600</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889852</v>
+        <v>125889841</v>
       </c>
       <c r="B17" t="n">
-        <v>88654</v>
+        <v>58027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401144</v>
+        <v>401024</v>
       </c>
       <c r="R17" t="n">
-        <v>7064600</v>
+        <v>7064328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889837</v>
+        <v>125889842</v>
       </c>
       <c r="B24" t="n">
-        <v>98382</v>
+        <v>91605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>2063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401214</v>
+        <v>401009</v>
       </c>
       <c r="R24" t="n">
-        <v>7064364</v>
+        <v>7064292</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889842</v>
+        <v>125889834</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
+        <v>91245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401009</v>
+        <v>401077</v>
       </c>
       <c r="R25" t="n">
-        <v>7064292</v>
+        <v>7064505</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889834</v>
+        <v>125889837</v>
       </c>
       <c r="B26" t="n">
-        <v>91245</v>
+        <v>98382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401077</v>
+        <v>401214</v>
       </c>
       <c r="R26" t="n">
-        <v>7064505</v>
+        <v>7064364</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125889844</v>
+        <v>125890348</v>
       </c>
       <c r="B30" t="n">
-        <v>91263</v>
+        <v>98382</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401002</v>
+        <v>401037</v>
       </c>
       <c r="R30" t="n">
-        <v>7064296</v>
+        <v>7064318</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,12 +3501,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3525,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889843</v>
+        <v>125889844</v>
       </c>
       <c r="B31" t="n">
         <v>91263</v>
@@ -3560,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401114</v>
+        <v>401002</v>
       </c>
       <c r="R31" t="n">
-        <v>7064640</v>
+        <v>7064296</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3622,32 +3628,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889833</v>
+        <v>125889843</v>
       </c>
       <c r="B32" t="n">
-        <v>91210</v>
+        <v>91263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3657,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401150</v>
+        <v>401114</v>
       </c>
       <c r="R32" t="n">
-        <v>7064603</v>
+        <v>7064640</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3719,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125890348</v>
+        <v>125889833</v>
       </c>
       <c r="B33" t="n">
-        <v>98382</v>
+        <v>91210</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3730,21 +3736,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3754,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401037</v>
+        <v>401150</v>
       </c>
       <c r="R33" t="n">
-        <v>7064318</v>
+        <v>7064603</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3792,18 +3798,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>75067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R3" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125890358</v>
+        <v>125889850</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401130</v>
+        <v>401064</v>
       </c>
       <c r="R4" t="n">
-        <v>7064629</v>
+        <v>7064314</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890366</v>
+        <v>125890358</v>
       </c>
       <c r="B5" t="n">
-        <v>75067</v>
+        <v>91263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401063</v>
+        <v>401130</v>
       </c>
       <c r="R5" t="n">
-        <v>7064359</v>
+        <v>7064629</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890351</v>
+        <v>125890363</v>
       </c>
       <c r="B8" t="n">
-        <v>80084</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401128</v>
+        <v>401196</v>
       </c>
       <c r="R8" t="n">
-        <v>7064635</v>
+        <v>7064572</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,32 +1373,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890352</v>
+        <v>125890357</v>
       </c>
       <c r="B9" t="n">
-        <v>79139</v>
+        <v>91263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1249</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401129</v>
+        <v>401016</v>
       </c>
       <c r="R9" t="n">
-        <v>7064590</v>
+        <v>7064444</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890363</v>
+        <v>125890351</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>80084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401196</v>
+        <v>401128</v>
       </c>
       <c r="R10" t="n">
-        <v>7064572</v>
+        <v>7064635</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890357</v>
+        <v>125890352</v>
       </c>
       <c r="B11" t="n">
-        <v>91263</v>
+        <v>79139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401016</v>
+        <v>401129</v>
       </c>
       <c r="R11" t="n">
-        <v>7064444</v>
+        <v>7064590</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125889848</v>
+        <v>125890341</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>75075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401108</v>
+        <v>401174</v>
       </c>
       <c r="R13" t="n">
-        <v>7064676</v>
+        <v>7064577</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125890341</v>
+        <v>125889848</v>
       </c>
       <c r="B14" t="n">
-        <v>75075</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1869,21 +1869,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>401174</v>
+        <v>401108</v>
       </c>
       <c r="R14" t="n">
-        <v>7064577</v>
+        <v>7064676</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889852</v>
+        <v>125889841</v>
       </c>
       <c r="B16" t="n">
-        <v>88654</v>
+        <v>58027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401144</v>
+        <v>401024</v>
       </c>
       <c r="R16" t="n">
-        <v>7064600</v>
+        <v>7064328</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889841</v>
+        <v>125889839</v>
       </c>
       <c r="B17" t="n">
-        <v>58027</v>
+        <v>98382</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2160,21 +2160,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401024</v>
+        <v>401042</v>
       </c>
       <c r="R17" t="n">
-        <v>7064328</v>
+        <v>7064326</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,6 +2220,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2246,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889839</v>
+        <v>125889852</v>
       </c>
       <c r="B18" t="n">
-        <v>98382</v>
+        <v>88654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401042</v>
+        <v>401144</v>
       </c>
       <c r="R18" t="n">
-        <v>7064326</v>
+        <v>7064600</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2317,11 +2322,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,32 +2445,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125889847</v>
+        <v>125890344</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>91942</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401042</v>
+        <v>401026</v>
       </c>
       <c r="R20" t="n">
         <v>7064458</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125890344</v>
+        <v>125889847</v>
       </c>
       <c r="B21" t="n">
-        <v>91942</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401026</v>
+        <v>401042</v>
       </c>
       <c r="R21" t="n">
         <v>7064458</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889842</v>
+        <v>125889834</v>
       </c>
       <c r="B24" t="n">
-        <v>91605</v>
+        <v>91245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2063</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401009</v>
+        <v>401077</v>
       </c>
       <c r="R24" t="n">
-        <v>7064292</v>
+        <v>7064505</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889834</v>
+        <v>125889842</v>
       </c>
       <c r="B25" t="n">
-        <v>91245</v>
+        <v>91605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2063</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401077</v>
+        <v>401009</v>
       </c>
       <c r="R25" t="n">
-        <v>7064505</v>
+        <v>7064292</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125890348</v>
+        <v>125889844</v>
       </c>
       <c r="B30" t="n">
-        <v>98382</v>
+        <v>91263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401037</v>
+        <v>401002</v>
       </c>
       <c r="R30" t="n">
-        <v>7064318</v>
+        <v>7064296</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,18 +3501,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3531,7 +3525,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889844</v>
+        <v>125889843</v>
       </c>
       <c r="B31" t="n">
         <v>91263</v>
@@ -3566,10 +3560,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401002</v>
+        <v>401114</v>
       </c>
       <c r="R31" t="n">
-        <v>7064296</v>
+        <v>7064640</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3628,32 +3622,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889843</v>
+        <v>125889833</v>
       </c>
       <c r="B32" t="n">
-        <v>91263</v>
+        <v>91210</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3657,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401114</v>
+        <v>401150</v>
       </c>
       <c r="R32" t="n">
-        <v>7064640</v>
+        <v>7064603</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,10 +3719,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125889833</v>
+        <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>91210</v>
+        <v>98382</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,21 +3730,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3760,10 +3754,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401150</v>
+        <v>401037</v>
       </c>
       <c r="R33" t="n">
-        <v>7064603</v>
+        <v>7064318</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3798,12 +3792,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4016,10 +4016,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125890353</v>
+        <v>125890365</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>75067</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,21 +4027,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401111</v>
+        <v>401081</v>
       </c>
       <c r="R36" t="n">
-        <v>7064685</v>
+        <v>7064302</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125890365</v>
+        <v>125890353</v>
       </c>
       <c r="B39" t="n">
-        <v>75067</v>
+        <v>80083</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>401081</v>
+        <v>401111</v>
       </c>
       <c r="R39" t="n">
-        <v>7064302</v>
+        <v>7064685</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -3428,32 +3428,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125889844</v>
+        <v>125890348</v>
       </c>
       <c r="B30" t="n">
-        <v>91263</v>
+        <v>98382</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401002</v>
+        <v>401037</v>
       </c>
       <c r="R30" t="n">
-        <v>7064296</v>
+        <v>7064318</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,12 +3501,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3525,7 +3531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889843</v>
+        <v>125889844</v>
       </c>
       <c r="B31" t="n">
         <v>91263</v>
@@ -3560,10 +3566,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401114</v>
+        <v>401002</v>
       </c>
       <c r="R31" t="n">
-        <v>7064640</v>
+        <v>7064296</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3622,32 +3628,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889833</v>
+        <v>125889843</v>
       </c>
       <c r="B32" t="n">
-        <v>91210</v>
+        <v>91263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3657,10 +3663,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401150</v>
+        <v>401114</v>
       </c>
       <c r="R32" t="n">
-        <v>7064603</v>
+        <v>7064640</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3719,10 +3725,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125890348</v>
+        <v>125889833</v>
       </c>
       <c r="B33" t="n">
-        <v>98382</v>
+        <v>91210</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3730,21 +3736,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3754,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401037</v>
+        <v>401150</v>
       </c>
       <c r="R33" t="n">
-        <v>7064318</v>
+        <v>7064603</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3792,18 +3798,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89601003</v>
+        <v>125890347</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bränthön, Jmt</t>
+          <t>Beljom, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401027.9987098145</v>
+        <v>401276</v>
       </c>
       <c r="R2" t="n">
-        <v>7064570.989134432</v>
+        <v>7064509</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,26 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125890366</v>
+        <v>125890365</v>
       </c>
       <c r="B3" t="n">
-        <v>75067</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401063</v>
+        <v>401081</v>
       </c>
       <c r="R3" t="n">
-        <v>7064359</v>
+        <v>7064302</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125889850</v>
+        <v>125890366</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401064</v>
+        <v>401063</v>
       </c>
       <c r="R4" t="n">
-        <v>7064314</v>
+        <v>7064359</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125890358</v>
+        <v>125889852</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401130</v>
+        <v>401144</v>
       </c>
       <c r="R5" t="n">
-        <v>7064629</v>
+        <v>7064600</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1082,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125889832</v>
+        <v>125889834</v>
       </c>
       <c r="B6" t="n">
-        <v>75075</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401085</v>
+        <v>401077</v>
       </c>
       <c r="R6" t="n">
-        <v>7064265</v>
+        <v>7064505</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125890359</v>
+        <v>125890352</v>
       </c>
       <c r="B7" t="n">
-        <v>91263</v>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1214,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>401146</v>
+        <v>401129</v>
       </c>
       <c r="R7" t="n">
-        <v>7064592</v>
+        <v>7064590</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1276,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125890363</v>
+        <v>125889842</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>92283</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401196</v>
+        <v>401009</v>
       </c>
       <c r="R8" t="n">
-        <v>7064572</v>
+        <v>7064292</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125890357</v>
+        <v>125890351</v>
       </c>
       <c r="B9" t="n">
-        <v>91263</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>401016</v>
+        <v>401128</v>
       </c>
       <c r="R9" t="n">
-        <v>7064444</v>
+        <v>7064635</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125890351</v>
+        <v>125890344</v>
       </c>
       <c r="B10" t="n">
-        <v>80084</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>401128</v>
+        <v>401026</v>
       </c>
       <c r="R10" t="n">
-        <v>7064635</v>
+        <v>7064458</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125890352</v>
+        <v>125889833</v>
       </c>
       <c r="B11" t="n">
-        <v>79139</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1249</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>401129</v>
+        <v>401150</v>
       </c>
       <c r="R11" t="n">
-        <v>7064590</v>
+        <v>7064603</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1664,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125889830</v>
+        <v>125890342</v>
       </c>
       <c r="B12" t="n">
-        <v>75075</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>401228</v>
+        <v>401266</v>
       </c>
       <c r="R12" t="n">
-        <v>7064385</v>
+        <v>7064514</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1761,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125890341</v>
+        <v>125889847</v>
       </c>
       <c r="B13" t="n">
-        <v>75075</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>401174</v>
+        <v>401042</v>
       </c>
       <c r="R13" t="n">
-        <v>7064577</v>
+        <v>7064458</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1861,11 +1842,11 @@
         <v>125889848</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1955,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125889831</v>
+        <v>125889849</v>
       </c>
       <c r="B15" t="n">
-        <v>75075</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>401096</v>
+        <v>401254</v>
       </c>
       <c r="R15" t="n">
-        <v>7064277</v>
+        <v>7064480</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125889841</v>
+        <v>125889850</v>
       </c>
       <c r="B16" t="n">
-        <v>58027</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>401024</v>
+        <v>401064</v>
       </c>
       <c r="R16" t="n">
-        <v>7064328</v>
+        <v>7064314</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2149,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125889839</v>
+        <v>125889851</v>
       </c>
       <c r="B17" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2184,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>401042</v>
+        <v>401035</v>
       </c>
       <c r="R17" t="n">
-        <v>7064326</v>
+        <v>7064310</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2220,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2251,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125889852</v>
+        <v>125890363</v>
       </c>
       <c r="B18" t="n">
-        <v>88654</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>401144</v>
+        <v>401196</v>
       </c>
       <c r="R18" t="n">
-        <v>7064600</v>
+        <v>7064572</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2348,48 +2324,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125889836</v>
+        <v>89601003</v>
       </c>
       <c r="B19" t="n">
-        <v>98382</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Beljom, Jmt</t>
+          <t>Bränthön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>401044</v>
+        <v>401028</v>
       </c>
       <c r="R19" t="n">
-        <v>7064691</v>
+        <v>7064571</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2413,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2433,44 +2409,48 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125890344</v>
+        <v>125889829</v>
       </c>
       <c r="B20" t="n">
-        <v>91942</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>401026</v>
+        <v>401164</v>
       </c>
       <c r="R20" t="n">
-        <v>7064458</v>
+        <v>7064559</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2542,10 +2522,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125889847</v>
+        <v>125889830</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,21 +2533,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>401042</v>
+        <v>401228</v>
       </c>
       <c r="R21" t="n">
-        <v>7064458</v>
+        <v>7064385</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2639,32 +2619,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125890350</v>
+        <v>125889831</v>
       </c>
       <c r="B22" t="n">
-        <v>98382</v>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2654,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>401071</v>
+        <v>401096</v>
       </c>
       <c r="R22" t="n">
-        <v>7064285</v>
+        <v>7064277</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2736,32 +2716,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125889838</v>
+        <v>125889832</v>
       </c>
       <c r="B23" t="n">
-        <v>98382</v>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>401179</v>
+        <v>401085</v>
       </c>
       <c r="R23" t="n">
-        <v>7064356</v>
+        <v>7064265</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2833,10 +2813,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125889834</v>
+        <v>125890340</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>83307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,21 +2824,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2848,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>401077</v>
+        <v>401087</v>
       </c>
       <c r="R24" t="n">
-        <v>7064505</v>
+        <v>7064246</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2906,12 +2886,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>7 st</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2930,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125889842</v>
+        <v>125890341</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2063</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>401009</v>
+        <v>401174</v>
       </c>
       <c r="R25" t="n">
-        <v>7064292</v>
+        <v>7064577</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3027,32 +3013,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125889837</v>
+        <v>125890353</v>
       </c>
       <c r="B26" t="n">
-        <v>98382</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>401214</v>
+        <v>401111</v>
       </c>
       <c r="R26" t="n">
-        <v>7064364</v>
+        <v>7064685</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3124,10 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125889849</v>
+        <v>125890345</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,34 +3121,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Beljom, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>401254</v>
+        <v>401083</v>
       </c>
       <c r="R27" t="n">
-        <v>7064480</v>
+        <v>7064287</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3195,6 +3189,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3221,32 +3220,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125889829</v>
+        <v>125889841</v>
       </c>
       <c r="B28" t="n">
-        <v>75075</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3255,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>401164</v>
+        <v>401024</v>
       </c>
       <c r="R28" t="n">
-        <v>7064559</v>
+        <v>7064328</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3318,53 +3317,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125890345</v>
+        <v>125889836</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>99140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Beljom, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>401083</v>
+        <v>401044</v>
       </c>
       <c r="R29" t="n">
-        <v>7064287</v>
+        <v>7064691</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3397,11 +3388,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3428,10 +3414,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125890348</v>
+        <v>125889837</v>
       </c>
       <c r="B30" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3463,10 +3449,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>401037</v>
+        <v>401214</v>
       </c>
       <c r="R30" t="n">
-        <v>7064318</v>
+        <v>7064364</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3501,18 +3487,12 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3531,32 +3511,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125889844</v>
+        <v>125889838</v>
       </c>
       <c r="B31" t="n">
-        <v>91263</v>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3566,10 +3546,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401002</v>
+        <v>401179</v>
       </c>
       <c r="R31" t="n">
-        <v>7064296</v>
+        <v>7064356</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3628,32 +3608,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125889843</v>
+        <v>125889839</v>
       </c>
       <c r="B32" t="n">
-        <v>91263</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3663,10 +3643,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401114</v>
+        <v>401042</v>
       </c>
       <c r="R32" t="n">
-        <v>7064640</v>
+        <v>7064326</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3699,6 +3679,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 30 plantor</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3725,10 +3710,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125889833</v>
+        <v>125890348</v>
       </c>
       <c r="B33" t="n">
-        <v>91210</v>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3736,21 +3721,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3760,10 +3745,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401150</v>
+        <v>401037</v>
       </c>
       <c r="R33" t="n">
-        <v>7064603</v>
+        <v>7064318</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3798,12 +3783,18 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>10 st</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3822,32 +3813,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125890347</v>
+        <v>125890350</v>
       </c>
       <c r="B34" t="n">
-        <v>91195</v>
+        <v>99140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3857,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401276</v>
+        <v>401071</v>
       </c>
       <c r="R34" t="n">
-        <v>7064509</v>
+        <v>7064285</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3916,491 +3907,6 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>125889851</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78980</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Beljom, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>401035</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7064310</v>
-      </c>
-      <c r="S35" t="n">
-        <v>15</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>125890365</v>
-      </c>
-      <c r="B36" t="n">
-        <v>75067</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>308</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Beljom, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>401081</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7064302</v>
-      </c>
-      <c r="S36" t="n">
-        <v>15</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>125890362</v>
-      </c>
-      <c r="B37" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Beljom, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>400981</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7064305</v>
-      </c>
-      <c r="S37" t="n">
-        <v>15</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>125890342</v>
-      </c>
-      <c r="B38" t="n">
-        <v>91210</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Beljom, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>401266</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7064514</v>
-      </c>
-      <c r="S38" t="n">
-        <v>15</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>125890353</v>
-      </c>
-      <c r="B39" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Beljom, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>401111</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7064685</v>
-      </c>
-      <c r="S39" t="n">
-        <v>15</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26003-2025 artfynd.xlsx
+++ b/artfynd/A 26003-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890347</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890365</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890366</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889852</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889834</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890352</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889842</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890351</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890344</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889833</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890342</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889847</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889848</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889849</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889850</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889851</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890363</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89601003</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2519,6 +2614,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889829</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2616,6 +2716,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889830</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889831</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2810,6 +2920,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889832</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890340</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3010,6 +3130,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890341</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3107,6 +3232,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890353</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3217,6 +3347,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890345</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3314,6 +3449,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889841</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3411,6 +3551,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889836</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3508,6 +3653,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889837</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3605,6 +3755,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889838</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3707,6 +3862,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125889839</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3810,6 +3970,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890348</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3907,8 +4072,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125890350</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>